--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:53:12+00:00</t>
+    <t>2026-08-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:08:45+00:00</t>
+    <t>2026-08-20T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T15:24:46+00:00</t>
+    <t>2026-08-21T08:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-23T21:45:18+00:00</t>
+    <t>2026-08-24T13:13:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -174,25 +174,19 @@
     <t>Patient.birthTime</t>
   </si>
   <si>
-    <t>FRLMPatient.deceased[x]:deceasedBoolean</t>
+    <t>FRLMPatient.deceased[x]</t>
   </si>
   <si>
     <t>Patient.sdtcDeceasedInd</t>
   </si>
   <si>
-    <t>FRLMPatient.deceased[x]:deceasedDateTime</t>
-  </si>
-  <si>
     <t>Patient.sdtcDeceasedTime</t>
   </si>
   <si>
-    <t>FRLMPatient.multipleBirth[x]:multipleBirthBoolean</t>
+    <t>FRLMPatient.multipleBirth[x]</t>
   </si>
   <si>
     <t>Patient.sdtcMultipleBirthInd</t>
-  </si>
-  <si>
-    <t>FRLMPatient.multipleBirth[x]:multipleBirthInteger</t>
   </si>
   <si>
     <t>Patient.sdtcMultipleBirthOrderNumber</t>
@@ -792,144 +786,144 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -962,7 +956,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -979,40 +973,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1054,7 +1048,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1069,7 +1063,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1082,7 +1076,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1095,7 +1089,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1108,7 +1102,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1121,7 +1115,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1134,7 +1128,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -1147,7 +1141,7 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -1160,7 +1154,7 @@
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1173,150 +1167,150 @@
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E22" s="2"/>
     </row>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="90">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:13:01+00:00</t>
+    <t>2026-08-25T11:34:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -216,12 +216,6 @@
     <t>FRLMPatient.contact.name</t>
   </si>
   <si>
-    <t>FRLMPatient.contact.name.family</t>
-  </si>
-  <si>
-    <t>FRLMPatient.contact.name.given</t>
-  </si>
-  <si>
     <t>FRLMPatient.contact.organization</t>
   </si>
   <si>
@@ -292,9 +286,6 @@
   </si>
   <si>
     <t>Patient.contact.name</t>
-  </si>
-  <si>
-    <t>related-to</t>
   </si>
   <si>
     <t>Patient.contact.organization</t>
@@ -695,7 +686,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -900,32 +891,6 @@
         <v>60</v>
       </c>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E17" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -956,7 +921,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -973,40 +938,40 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1017,7 +982,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1048,7 +1013,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1063,7 +1028,7 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -1076,7 +1041,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -1089,7 +1054,7 @@
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2"/>
     </row>
@@ -1102,7 +1067,7 @@
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -1115,7 +1080,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -1128,7 +1093,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -1141,7 +1106,7 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E9" s="2"/>
     </row>
@@ -1154,7 +1119,7 @@
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E10" s="2"/>
     </row>
@@ -1167,39 +1132,39 @@
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -1212,7 +1177,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
@@ -1225,7 +1190,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -1238,7 +1203,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -1251,7 +1216,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -1261,58 +1226,6 @@
         <v>89</v>
       </c>
       <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B21" s="2"/>
-      <c r="C21" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="D21" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="B22" s="2"/>
-      <c r="C22" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="D22" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="E22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:34:21+00:00</t>
+    <t>2026-08-25T11:56:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T11:56:50+00:00</t>
+    <t>2026-08-25T20:08:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
+++ b/fix-target-codes-and-display/ig/FRPatientLMCDAFHIR.xlsx
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-25T20:08:46+00:00</t>
+    <t>2026-08-31T08:09:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
